--- a/tests/fixtures/xlsx-viewer/f8-small.xlsx
+++ b/tests/fixtures/xlsx-viewer/f8-small.xlsx
@@ -104,6 +104,28 @@
       <c r="A4" s="2">
         <v>7</v>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>a_x000D_b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="1">
+        <is>
+          <t>t-name</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="1">
+        <is>
+          <t>t-value</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="1">
+        <is>
+          <t>t-total</t>
+        </is>
+      </c>
     </row>
     <row r="1048576">
       <c r="XFD1048576" t="inlineStr">
